--- a/codigos/table.xlsx
+++ b/codigos/table.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ciro\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ciro\Documents\tesis_maestria\codigos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F90C6DD-E52D-411D-9AE3-756C6BEB74B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5043B96-B7CD-49C4-ABB1-8D4701481C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B4B41839-16A5-44F8-BFA4-296AA16889C7}"/>
+    <workbookView xWindow="29610" yWindow="-10095" windowWidth="9720" windowHeight="8970" activeTab="1" xr2:uid="{B4B41839-16A5-44F8-BFA4-296AA16889C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>FPGA</t>
   </si>
@@ -161,6 +162,33 @@
   </si>
   <si>
     <t>350/256</t>
+  </si>
+  <si>
+    <t>Los datos son aleatorios (H0 es verdadera)</t>
+  </si>
+  <si>
+    <t>Los datos no son aleatorios (Ha es verdadera)</t>
+  </si>
+  <si>
+    <t>Aceptar H0</t>
+  </si>
+  <si>
+    <t>Aceptar Ha (rechazar H0)</t>
+  </si>
+  <si>
+    <t>No error</t>
+  </si>
+  <si>
+    <t>Error de Tipo II</t>
+  </si>
+  <si>
+    <t>Error de Tipo I</t>
+  </si>
+  <si>
+    <t>SITUACIÓN VERDADERA</t>
+  </si>
+  <si>
+    <t>CONCLUSIÓN</t>
   </si>
 </sst>
 </file>
@@ -168,7 +196,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -288,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -305,25 +333,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -704,7 +735,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -728,12 +759,12 @@
       <c r="H3" s="6">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="13">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
@@ -755,10 +786,10 @@
       <c r="H4" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
@@ -780,10 +811,10 @@
       <c r="H5" s="10">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -807,12 +838,12 @@
       <c r="H6" s="6">
         <v>0.53900000000000003</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
@@ -834,10 +865,10 @@
       <c r="H7" s="8">
         <v>1.4379999999999999</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
@@ -859,10 +890,10 @@
       <c r="H8" s="10">
         <v>0.32700000000000001</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -886,12 +917,12 @@
       <c r="H9" s="6">
         <v>2.5670000000000002</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
@@ -913,10 +944,10 @@
       <c r="H10" s="8">
         <v>2.1970000000000001</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
@@ -938,10 +969,10 @@
       <c r="H11" s="10">
         <v>3.6160000000000001</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -965,12 +996,12 @@
       <c r="H12" s="6">
         <v>0.43099999999999999</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
@@ -992,10 +1023,10 @@
       <c r="H13" s="8">
         <v>0.59199999999999997</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="4" t="s">
         <v>23</v>
       </c>
@@ -1017,10 +1048,10 @@
       <c r="H14" s="10">
         <v>0.34</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1044,12 +1075,12 @@
       <c r="H15" s="6">
         <v>0.624</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1071,10 +1102,10 @@
       <c r="H16" s="8">
         <v>0.98499999999999999</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
@@ -1096,10 +1127,10 @@
       <c r="H17" s="10">
         <v>0.999</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1123,12 +1154,12 @@
       <c r="H18" s="6">
         <v>154.12100000000001</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1150,10 +1181,10 @@
       <c r="H19" s="8">
         <v>244.755</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
@@ -1175,15 +1206,10 @@
       <c r="H20" s="10">
         <v>188.52199999999999</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I15:I17"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
@@ -1191,6 +1217,70 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I15:I17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971791AF-8F88-4795-95CB-0248910A7AF5}">
+  <dimension ref="A6:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="13"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
